--- a/excels/IPCRTest.xlsx
+++ b/excels/IPCRTest.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
@@ -470,40 +470,44 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -511,11 +515,11 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -523,91 +527,91 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="13" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="13" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="14" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="14" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -630,15 +634,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>297360</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>261360</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>73080</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>330480</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>66240</xdr:rowOff>
+      <xdr:colOff>294120</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>138960</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -651,8 +655,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4577760" y="181080"/>
-          <a:ext cx="644760" cy="609120"/>
+          <a:off x="4541760" y="73080"/>
+          <a:ext cx="644400" cy="608760"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -669,14 +673,14 @@
     <xdr:from>
       <xdr:col>11</xdr:col>
       <xdr:colOff>198000</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>37080</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>267840</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>101880</xdr:rowOff>
+      <xdr:colOff>267480</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>138600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -689,8 +693,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7558200" y="181080"/>
-          <a:ext cx="681480" cy="644760"/>
+          <a:off x="7558200" y="37080"/>
+          <a:ext cx="681120" cy="644400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -886,758 +890,758 @@
   <dimension ref="A1:S32"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="17.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="17.77"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="2.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="17.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="17.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="2.31"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
-      <c r="O2" s="1"/>
-      <c r="P2" s="1"/>
-      <c r="Q2" s="1"/>
-      <c r="R2" s="1"/>
-      <c r="S2" s="1"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
+      <c r="S2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2"/>
-      <c r="O3" s="2"/>
-      <c r="P3" s="2"/>
-      <c r="Q3" s="2"/>
-      <c r="R3" s="2"/>
-      <c r="S3" s="2"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
+      <c r="P3" s="3"/>
+      <c r="Q3" s="3"/>
+      <c r="R3" s="3"/>
+      <c r="S3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2"/>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2"/>
-      <c r="Q4" s="2"/>
-      <c r="R4" s="2"/>
-      <c r="S4" s="2"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3"/>
+      <c r="O4" s="3"/>
+      <c r="P4" s="3"/>
+      <c r="Q4" s="3"/>
+      <c r="R4" s="3"/>
+      <c r="S4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
-      <c r="N5" s="3"/>
-      <c r="O5" s="3"/>
-      <c r="P5" s="3"/>
-      <c r="Q5" s="3"/>
-      <c r="R5" s="3"/>
-      <c r="S5" s="3"/>
-    </row>
-    <row r="6" customFormat="false" ht="11.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+      <c r="M5" s="4"/>
+      <c r="N5" s="4"/>
+      <c r="O5" s="4"/>
+      <c r="P5" s="4"/>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="4"/>
+      <c r="S5" s="4"/>
+    </row>
+    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="4"/>
-      <c r="M6" s="4"/>
-      <c r="N6" s="4"/>
-      <c r="O6" s="4"/>
-      <c r="P6" s="4"/>
-      <c r="Q6" s="4"/>
-      <c r="R6" s="4"/>
-      <c r="S6" s="4"/>
-    </row>
-    <row r="7" customFormat="false" ht="11.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="5"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="5"/>
+      <c r="Q6" s="5"/>
+      <c r="R6" s="5"/>
+      <c r="S6" s="5"/>
+    </row>
+    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5"/>
-      <c r="M7" s="5"/>
-      <c r="N7" s="5"/>
-      <c r="O7" s="5"/>
-      <c r="P7" s="5"/>
-      <c r="Q7" s="5"/>
-      <c r="R7" s="5"/>
-      <c r="S7" s="5"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="6"/>
+      <c r="O7" s="6"/>
+      <c r="P7" s="6"/>
+      <c r="Q7" s="6"/>
+      <c r="R7" s="6"/>
+      <c r="S7" s="6"/>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="6"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="6"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="2" t="s">
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
+      <c r="N8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="O8" s="2"/>
-      <c r="P8" s="2"/>
-      <c r="Q8" s="2"/>
-      <c r="R8" s="2"/>
-      <c r="S8" s="2"/>
+      <c r="O8" s="3"/>
+      <c r="P8" s="3"/>
+      <c r="Q8" s="3"/>
+      <c r="R8" s="3"/>
+      <c r="S8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="6"/>
-      <c r="K9" s="6"/>
-      <c r="L9" s="6"/>
-      <c r="M9" s="6"/>
-      <c r="N9" s="7" t="s">
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="7"/>
+      <c r="N9" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="O9" s="7"/>
-      <c r="P9" s="7"/>
-      <c r="Q9" s="7"/>
-      <c r="R9" s="7"/>
-      <c r="S9" s="7"/>
+      <c r="O9" s="8"/>
+      <c r="P9" s="8"/>
+      <c r="Q9" s="8"/>
+      <c r="R9" s="8"/>
+      <c r="S9" s="8"/>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6"/>
-      <c r="J10" s="6"/>
-      <c r="K10" s="6"/>
-      <c r="L10" s="6"/>
-      <c r="M10" s="6"/>
-      <c r="N10" s="1"/>
-      <c r="O10" s="1"/>
-      <c r="P10" s="1"/>
-      <c r="Q10" s="1"/>
-      <c r="R10" s="1"/>
-      <c r="S10" s="1"/>
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="7"/>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="2"/>
+      <c r="R10" s="2"/>
+      <c r="S10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="6"/>
-      <c r="K11" s="6"/>
-      <c r="L11" s="6"/>
-      <c r="M11" s="6"/>
-      <c r="N11" s="7" t="s">
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="7"/>
+      <c r="N11" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="O11" s="7"/>
-      <c r="P11" s="7"/>
-      <c r="Q11" s="7"/>
-      <c r="R11" s="7"/>
-      <c r="S11" s="7"/>
+      <c r="O11" s="8"/>
+      <c r="P11" s="8"/>
+      <c r="Q11" s="8"/>
+      <c r="R11" s="8"/>
+      <c r="S11" s="8"/>
     </row>
     <row r="12" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="9" t="s">
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="I12" s="9"/>
-      <c r="J12" s="8" t="s">
+      <c r="I12" s="10"/>
+      <c r="J12" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="K12" s="8"/>
-      <c r="L12" s="8"/>
-      <c r="M12" s="8"/>
-      <c r="N12" s="8"/>
-      <c r="O12" s="8"/>
-      <c r="P12" s="8"/>
-      <c r="Q12" s="8"/>
-      <c r="R12" s="10" t="s">
+      <c r="K12" s="9"/>
+      <c r="L12" s="9"/>
+      <c r="M12" s="9"/>
+      <c r="N12" s="9"/>
+      <c r="O12" s="9"/>
+      <c r="P12" s="9"/>
+      <c r="Q12" s="9"/>
+      <c r="R12" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="S12" s="10"/>
+      <c r="S12" s="11"/>
     </row>
     <row r="13" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="12"/>
-      <c r="J13" s="11" t="s">
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="13"/>
+      <c r="I13" s="13"/>
+      <c r="J13" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="K13" s="11"/>
-      <c r="L13" s="11"/>
-      <c r="M13" s="11"/>
-      <c r="N13" s="11"/>
-      <c r="O13" s="11"/>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="11"/>
-      <c r="R13" s="13"/>
-      <c r="S13" s="13"/>
+      <c r="K13" s="12"/>
+      <c r="L13" s="12"/>
+      <c r="M13" s="12"/>
+      <c r="N13" s="12"/>
+      <c r="O13" s="12"/>
+      <c r="P13" s="12"/>
+      <c r="Q13" s="12"/>
+      <c r="R13" s="14"/>
+      <c r="S13" s="14"/>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="14" t="s">
+      <c r="A14" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="12"/>
-      <c r="J14" s="14" t="s">
+      <c r="B14" s="15"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="13"/>
+      <c r="I14" s="13"/>
+      <c r="J14" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="K14" s="14"/>
-      <c r="L14" s="14"/>
-      <c r="M14" s="14"/>
-      <c r="N14" s="14"/>
-      <c r="O14" s="14"/>
-      <c r="P14" s="14"/>
-      <c r="Q14" s="14"/>
-      <c r="R14" s="13"/>
-      <c r="S14" s="13"/>
+      <c r="K14" s="15"/>
+      <c r="L14" s="15"/>
+      <c r="M14" s="15"/>
+      <c r="N14" s="15"/>
+      <c r="O14" s="15"/>
+      <c r="P14" s="15"/>
+      <c r="Q14" s="15"/>
+      <c r="R14" s="14"/>
+      <c r="S14" s="14"/>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
-      <c r="J15" s="6"/>
-      <c r="K15" s="6"/>
-      <c r="L15" s="6"/>
-      <c r="M15" s="6"/>
-      <c r="N15" s="6"/>
-      <c r="O15" s="6"/>
-      <c r="P15" s="6"/>
-      <c r="Q15" s="6"/>
-      <c r="R15" s="6"/>
-      <c r="S15" s="6"/>
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="7"/>
+      <c r="M15" s="7"/>
+      <c r="N15" s="7"/>
+      <c r="O15" s="7"/>
+      <c r="P15" s="7"/>
+      <c r="Q15" s="7"/>
+      <c r="R15" s="7"/>
+      <c r="S15" s="7"/>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
-      <c r="J16" s="6"/>
-      <c r="K16" s="6"/>
-      <c r="L16" s="6"/>
-      <c r="M16" s="6"/>
-      <c r="N16" s="6"/>
-      <c r="O16" s="15" t="s">
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="7"/>
+      <c r="J16" s="7"/>
+      <c r="K16" s="7"/>
+      <c r="L16" s="7"/>
+      <c r="M16" s="7"/>
+      <c r="N16" s="7"/>
+      <c r="O16" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="P16" s="15"/>
-      <c r="Q16" s="16" t="s">
+      <c r="P16" s="16"/>
+      <c r="Q16" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="R16" s="17" t="s">
+      <c r="R16" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="S16" s="17"/>
+      <c r="S16" s="18"/>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6"/>
-      <c r="J17" s="6"/>
-      <c r="K17" s="6"/>
-      <c r="L17" s="6"/>
-      <c r="M17" s="6"/>
-      <c r="N17" s="6"/>
-      <c r="O17" s="6"/>
-      <c r="P17" s="6"/>
-      <c r="Q17" s="18" t="s">
+      <c r="A17" s="7"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7"/>
+      <c r="J17" s="7"/>
+      <c r="K17" s="7"/>
+      <c r="L17" s="7"/>
+      <c r="M17" s="7"/>
+      <c r="N17" s="7"/>
+      <c r="O17" s="7"/>
+      <c r="P17" s="7"/>
+      <c r="Q17" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="R17" s="19" t="s">
+      <c r="R17" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="S17" s="19"/>
+      <c r="S17" s="20"/>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
-      <c r="K18" s="6"/>
-      <c r="L18" s="6"/>
-      <c r="M18" s="6"/>
-      <c r="N18" s="6"/>
-      <c r="O18" s="6"/>
-      <c r="P18" s="6"/>
-      <c r="Q18" s="18" t="s">
+      <c r="A18" s="7"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="7"/>
+      <c r="K18" s="7"/>
+      <c r="L18" s="7"/>
+      <c r="M18" s="7"/>
+      <c r="N18" s="7"/>
+      <c r="O18" s="7"/>
+      <c r="P18" s="7"/>
+      <c r="Q18" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="R18" s="19" t="s">
+      <c r="R18" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="S18" s="19"/>
+      <c r="S18" s="20"/>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="6"/>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6"/>
-      <c r="J19" s="6"/>
-      <c r="K19" s="6"/>
-      <c r="L19" s="6"/>
-      <c r="M19" s="6"/>
-      <c r="N19" s="6"/>
-      <c r="O19" s="6"/>
-      <c r="P19" s="6"/>
-      <c r="Q19" s="18" t="s">
+      <c r="A19" s="7"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="7"/>
+      <c r="J19" s="7"/>
+      <c r="K19" s="7"/>
+      <c r="L19" s="7"/>
+      <c r="M19" s="7"/>
+      <c r="N19" s="7"/>
+      <c r="O19" s="7"/>
+      <c r="P19" s="7"/>
+      <c r="Q19" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="R19" s="19" t="s">
+      <c r="R19" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="S19" s="19"/>
+      <c r="S19" s="20"/>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="6"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6"/>
-      <c r="J20" s="6"/>
-      <c r="K20" s="6"/>
-      <c r="L20" s="6"/>
-      <c r="M20" s="6"/>
-      <c r="N20" s="6"/>
-      <c r="O20" s="6"/>
-      <c r="P20" s="6"/>
-      <c r="Q20" s="20" t="s">
+      <c r="A20" s="7"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7"/>
+      <c r="I20" s="7"/>
+      <c r="J20" s="7"/>
+      <c r="K20" s="7"/>
+      <c r="L20" s="7"/>
+      <c r="M20" s="7"/>
+      <c r="N20" s="7"/>
+      <c r="O20" s="7"/>
+      <c r="P20" s="7"/>
+      <c r="Q20" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="R20" s="21" t="s">
+      <c r="R20" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="S20" s="21"/>
+      <c r="S20" s="22"/>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="6"/>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6"/>
-      <c r="J21" s="6"/>
-      <c r="K21" s="6"/>
-      <c r="L21" s="6"/>
-      <c r="M21" s="6"/>
-      <c r="N21" s="6"/>
-      <c r="O21" s="6"/>
-      <c r="P21" s="6"/>
-      <c r="Q21" s="6"/>
-      <c r="R21" s="6"/>
-      <c r="S21" s="6"/>
+      <c r="A21" s="7"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
+      <c r="H21" s="7"/>
+      <c r="I21" s="7"/>
+      <c r="J21" s="7"/>
+      <c r="K21" s="7"/>
+      <c r="L21" s="7"/>
+      <c r="M21" s="7"/>
+      <c r="N21" s="7"/>
+      <c r="O21" s="7"/>
+      <c r="P21" s="7"/>
+      <c r="Q21" s="7"/>
+      <c r="R21" s="7"/>
+      <c r="S21" s="7"/>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="22" t="s">
+      <c r="A22" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="B22" s="22"/>
-      <c r="C22" s="22"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="22"/>
-      <c r="F22" s="23" t="s">
+      <c r="B22" s="23"/>
+      <c r="C22" s="23"/>
+      <c r="D22" s="23"/>
+      <c r="E22" s="23"/>
+      <c r="F22" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="G22" s="23"/>
-      <c r="H22" s="23"/>
-      <c r="I22" s="23"/>
-      <c r="J22" s="24" t="s">
+      <c r="G22" s="24"/>
+      <c r="H22" s="24"/>
+      <c r="I22" s="24"/>
+      <c r="J22" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="K22" s="24"/>
-      <c r="L22" s="24"/>
-      <c r="M22" s="24"/>
-      <c r="N22" s="25" t="s">
+      <c r="K22" s="25"/>
+      <c r="L22" s="25"/>
+      <c r="M22" s="25"/>
+      <c r="N22" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="O22" s="25"/>
-      <c r="P22" s="25"/>
-      <c r="Q22" s="25"/>
-      <c r="R22" s="22" t="s">
+      <c r="O22" s="26"/>
+      <c r="P22" s="26"/>
+      <c r="Q22" s="26"/>
+      <c r="R22" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="S22" s="22"/>
+      <c r="S22" s="23"/>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="22"/>
-      <c r="B23" s="22"/>
-      <c r="C23" s="22"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="22"/>
-      <c r="F23" s="23"/>
-      <c r="G23" s="23"/>
-      <c r="H23" s="23"/>
-      <c r="I23" s="23"/>
-      <c r="J23" s="24"/>
-      <c r="K23" s="24"/>
-      <c r="L23" s="24"/>
-      <c r="M23" s="24"/>
-      <c r="N23" s="25"/>
-      <c r="O23" s="25"/>
-      <c r="P23" s="25"/>
-      <c r="Q23" s="25"/>
-      <c r="R23" s="22"/>
-      <c r="S23" s="22"/>
+      <c r="A23" s="23"/>
+      <c r="B23" s="23"/>
+      <c r="C23" s="23"/>
+      <c r="D23" s="23"/>
+      <c r="E23" s="23"/>
+      <c r="F23" s="24"/>
+      <c r="G23" s="24"/>
+      <c r="H23" s="24"/>
+      <c r="I23" s="24"/>
+      <c r="J23" s="25"/>
+      <c r="K23" s="25"/>
+      <c r="L23" s="25"/>
+      <c r="M23" s="25"/>
+      <c r="N23" s="26"/>
+      <c r="O23" s="26"/>
+      <c r="P23" s="26"/>
+      <c r="Q23" s="26"/>
+      <c r="R23" s="23"/>
+      <c r="S23" s="23"/>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="22"/>
-      <c r="B24" s="22"/>
-      <c r="C24" s="22"/>
-      <c r="D24" s="22"/>
-      <c r="E24" s="22"/>
-      <c r="F24" s="23"/>
-      <c r="G24" s="23"/>
-      <c r="H24" s="23"/>
-      <c r="I24" s="23"/>
-      <c r="J24" s="24"/>
-      <c r="K24" s="24"/>
-      <c r="L24" s="24"/>
-      <c r="M24" s="24"/>
-      <c r="N24" s="26" t="s">
+      <c r="A24" s="23"/>
+      <c r="B24" s="23"/>
+      <c r="C24" s="23"/>
+      <c r="D24" s="23"/>
+      <c r="E24" s="23"/>
+      <c r="F24" s="24"/>
+      <c r="G24" s="24"/>
+      <c r="H24" s="24"/>
+      <c r="I24" s="24"/>
+      <c r="J24" s="25"/>
+      <c r="K24" s="25"/>
+      <c r="L24" s="25"/>
+      <c r="M24" s="25"/>
+      <c r="N24" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="O24" s="26" t="s">
+      <c r="O24" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="P24" s="26" t="s">
+      <c r="P24" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="Q24" s="26" t="s">
+      <c r="Q24" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="R24" s="22"/>
-      <c r="S24" s="22"/>
+      <c r="R24" s="23"/>
+      <c r="S24" s="23"/>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="27" t="s">
+      <c r="A25" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="B25" s="27"/>
-      <c r="C25" s="27"/>
-      <c r="D25" s="27"/>
-      <c r="E25" s="27"/>
-      <c r="F25" s="27"/>
-      <c r="G25" s="27"/>
-      <c r="H25" s="27"/>
-      <c r="I25" s="27"/>
-      <c r="J25" s="27"/>
-      <c r="K25" s="27"/>
-      <c r="L25" s="27"/>
-      <c r="M25" s="27"/>
-      <c r="N25" s="28"/>
-      <c r="O25" s="28"/>
-      <c r="P25" s="28"/>
-      <c r="Q25" s="28"/>
-      <c r="R25" s="29"/>
-      <c r="S25" s="29"/>
+      <c r="B25" s="28"/>
+      <c r="C25" s="28"/>
+      <c r="D25" s="28"/>
+      <c r="E25" s="28"/>
+      <c r="F25" s="28"/>
+      <c r="G25" s="28"/>
+      <c r="H25" s="28"/>
+      <c r="I25" s="28"/>
+      <c r="J25" s="28"/>
+      <c r="K25" s="28"/>
+      <c r="L25" s="28"/>
+      <c r="M25" s="28"/>
+      <c r="N25" s="29"/>
+      <c r="O25" s="29"/>
+      <c r="P25" s="29"/>
+      <c r="Q25" s="29"/>
+      <c r="R25" s="30"/>
+      <c r="S25" s="30"/>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="8" t="s">
+      <c r="A26" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
-      <c r="G26" s="8"/>
-      <c r="H26" s="8"/>
-      <c r="I26" s="8"/>
-      <c r="J26" s="8"/>
-      <c r="K26" s="8"/>
-      <c r="L26" s="8"/>
-      <c r="M26" s="8"/>
-      <c r="N26" s="8"/>
-      <c r="O26" s="8"/>
-      <c r="P26" s="8"/>
-      <c r="Q26" s="8"/>
-      <c r="R26" s="8"/>
-      <c r="S26" s="8"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="9"/>
+      <c r="I26" s="9"/>
+      <c r="J26" s="9"/>
+      <c r="K26" s="9"/>
+      <c r="L26" s="9"/>
+      <c r="M26" s="9"/>
+      <c r="N26" s="9"/>
+      <c r="O26" s="9"/>
+      <c r="P26" s="9"/>
+      <c r="Q26" s="9"/>
+      <c r="R26" s="9"/>
+      <c r="S26" s="9"/>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="30"/>
-      <c r="B27" s="30"/>
-      <c r="C27" s="30"/>
-      <c r="D27" s="30"/>
-      <c r="E27" s="30"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="31"/>
-      <c r="H27" s="31"/>
-      <c r="I27" s="31"/>
-      <c r="J27" s="6"/>
-      <c r="K27" s="31"/>
-      <c r="L27" s="31"/>
-      <c r="M27" s="31"/>
-      <c r="N27" s="32"/>
-      <c r="O27" s="32"/>
-      <c r="P27" s="32"/>
-      <c r="Q27" s="32"/>
-      <c r="R27" s="6"/>
-      <c r="S27" s="6"/>
+      <c r="A27" s="31"/>
+      <c r="B27" s="31"/>
+      <c r="C27" s="31"/>
+      <c r="D27" s="31"/>
+      <c r="E27" s="31"/>
+      <c r="F27" s="7"/>
+      <c r="G27" s="32"/>
+      <c r="H27" s="32"/>
+      <c r="I27" s="32"/>
+      <c r="J27" s="7"/>
+      <c r="K27" s="32"/>
+      <c r="L27" s="32"/>
+      <c r="M27" s="32"/>
+      <c r="N27" s="33"/>
+      <c r="O27" s="33"/>
+      <c r="P27" s="33"/>
+      <c r="Q27" s="33"/>
+      <c r="R27" s="7"/>
+      <c r="S27" s="7"/>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="30"/>
-      <c r="B28" s="30"/>
-      <c r="C28" s="30"/>
-      <c r="D28" s="30"/>
-      <c r="E28" s="30"/>
-      <c r="F28" s="6"/>
-      <c r="G28" s="31"/>
-      <c r="H28" s="31"/>
-      <c r="I28" s="31"/>
-      <c r="J28" s="6"/>
-      <c r="K28" s="31"/>
-      <c r="L28" s="31"/>
-      <c r="M28" s="31"/>
-      <c r="N28" s="32"/>
-      <c r="O28" s="32"/>
-      <c r="P28" s="32"/>
-      <c r="Q28" s="32"/>
-      <c r="R28" s="6"/>
-      <c r="S28" s="6"/>
+      <c r="A28" s="31"/>
+      <c r="B28" s="31"/>
+      <c r="C28" s="31"/>
+      <c r="D28" s="31"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="32"/>
+      <c r="H28" s="32"/>
+      <c r="I28" s="32"/>
+      <c r="J28" s="7"/>
+      <c r="K28" s="32"/>
+      <c r="L28" s="32"/>
+      <c r="M28" s="32"/>
+      <c r="N28" s="33"/>
+      <c r="O28" s="33"/>
+      <c r="P28" s="33"/>
+      <c r="Q28" s="33"/>
+      <c r="R28" s="7"/>
+      <c r="S28" s="7"/>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="30"/>
-      <c r="B29" s="30"/>
-      <c r="C29" s="30"/>
-      <c r="D29" s="30"/>
-      <c r="E29" s="30"/>
-      <c r="F29" s="6"/>
-      <c r="G29" s="33"/>
-      <c r="H29" s="33"/>
-      <c r="I29" s="33"/>
-      <c r="J29" s="6"/>
-      <c r="K29" s="33"/>
-      <c r="L29" s="33"/>
-      <c r="M29" s="33"/>
-      <c r="N29" s="32"/>
-      <c r="O29" s="32"/>
-      <c r="P29" s="32"/>
-      <c r="Q29" s="32"/>
-      <c r="R29" s="6"/>
-      <c r="S29" s="6"/>
+      <c r="A29" s="31"/>
+      <c r="B29" s="31"/>
+      <c r="C29" s="31"/>
+      <c r="D29" s="31"/>
+      <c r="E29" s="31"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="34"/>
+      <c r="H29" s="34"/>
+      <c r="I29" s="34"/>
+      <c r="J29" s="7"/>
+      <c r="K29" s="34"/>
+      <c r="L29" s="34"/>
+      <c r="M29" s="34"/>
+      <c r="N29" s="33"/>
+      <c r="O29" s="33"/>
+      <c r="P29" s="33"/>
+      <c r="Q29" s="33"/>
+      <c r="R29" s="7"/>
+      <c r="S29" s="7"/>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="30"/>
-      <c r="B30" s="30"/>
-      <c r="C30" s="30"/>
-      <c r="D30" s="30"/>
-      <c r="E30" s="30"/>
-      <c r="F30" s="6"/>
-      <c r="G30" s="33"/>
-      <c r="H30" s="33"/>
-      <c r="I30" s="33"/>
-      <c r="J30" s="6"/>
-      <c r="K30" s="33"/>
-      <c r="L30" s="33"/>
-      <c r="M30" s="33"/>
-      <c r="N30" s="32"/>
-      <c r="O30" s="32"/>
-      <c r="P30" s="32"/>
-      <c r="Q30" s="32"/>
-      <c r="R30" s="6"/>
-      <c r="S30" s="6"/>
+      <c r="A30" s="31"/>
+      <c r="B30" s="31"/>
+      <c r="C30" s="31"/>
+      <c r="D30" s="31"/>
+      <c r="E30" s="31"/>
+      <c r="F30" s="7"/>
+      <c r="G30" s="34"/>
+      <c r="H30" s="34"/>
+      <c r="I30" s="34"/>
+      <c r="J30" s="7"/>
+      <c r="K30" s="34"/>
+      <c r="L30" s="34"/>
+      <c r="M30" s="34"/>
+      <c r="N30" s="33"/>
+      <c r="O30" s="33"/>
+      <c r="P30" s="33"/>
+      <c r="Q30" s="33"/>
+      <c r="R30" s="7"/>
+      <c r="S30" s="7"/>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="30"/>
-      <c r="B31" s="30"/>
-      <c r="C31" s="30"/>
-      <c r="D31" s="30"/>
-      <c r="E31" s="30"/>
-      <c r="G31" s="34"/>
-      <c r="H31" s="34"/>
-      <c r="I31" s="34"/>
-      <c r="K31" s="34"/>
-      <c r="L31" s="34"/>
-      <c r="M31" s="34"/>
-      <c r="N31" s="32"/>
-      <c r="O31" s="32"/>
-      <c r="P31" s="32"/>
-      <c r="Q31" s="32"/>
-      <c r="R31" s="6"/>
-      <c r="S31" s="6"/>
+      <c r="A31" s="31"/>
+      <c r="B31" s="31"/>
+      <c r="C31" s="31"/>
+      <c r="D31" s="31"/>
+      <c r="E31" s="31"/>
+      <c r="G31" s="35"/>
+      <c r="H31" s="35"/>
+      <c r="I31" s="35"/>
+      <c r="K31" s="35"/>
+      <c r="L31" s="35"/>
+      <c r="M31" s="35"/>
+      <c r="N31" s="33"/>
+      <c r="O31" s="33"/>
+      <c r="P31" s="33"/>
+      <c r="Q31" s="33"/>
+      <c r="R31" s="7"/>
+      <c r="S31" s="7"/>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="30"/>
-      <c r="B32" s="30"/>
-      <c r="C32" s="30"/>
-      <c r="D32" s="30"/>
-      <c r="E32" s="30"/>
-      <c r="G32" s="34"/>
-      <c r="H32" s="34"/>
-      <c r="I32" s="34"/>
-      <c r="K32" s="34"/>
-      <c r="L32" s="34"/>
-      <c r="M32" s="34"/>
-      <c r="N32" s="32"/>
-      <c r="O32" s="32"/>
-      <c r="P32" s="32"/>
-      <c r="Q32" s="32"/>
-      <c r="R32" s="6"/>
-      <c r="S32" s="6"/>
+      <c r="A32" s="31"/>
+      <c r="B32" s="31"/>
+      <c r="C32" s="31"/>
+      <c r="D32" s="31"/>
+      <c r="E32" s="31"/>
+      <c r="G32" s="35"/>
+      <c r="H32" s="35"/>
+      <c r="I32" s="35"/>
+      <c r="K32" s="35"/>
+      <c r="L32" s="35"/>
+      <c r="M32" s="35"/>
+      <c r="N32" s="33"/>
+      <c r="O32" s="33"/>
+      <c r="P32" s="33"/>
+      <c r="Q32" s="33"/>
+      <c r="R32" s="7"/>
+      <c r="S32" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="35">
